--- a/onagawa_water_tariff/10_wbs/onagawa_wbs_R8.xlsx
+++ b/onagawa_water_tariff/10_wbs/onagawa_wbs_R8.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_仕様書対応" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'01_WBS'!$A$5:$I$74</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'01_WBS'!$A$5:$I$78</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -617,7 +617,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J81"/>
+  <dimension ref="A1:J85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2265,39 +2265,65 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="19" customHeight="1">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B43" s="5" t="inlineStr">
-        <is>
-          <t>料金改定シミュレーション</t>
-        </is>
-      </c>
-      <c r="C43" s="6" t="n"/>
-      <c r="D43" s="6" t="n"/>
-      <c r="E43" s="6" t="n"/>
-      <c r="F43" s="6" t="n"/>
-      <c r="G43" s="6" t="n"/>
-      <c r="H43" s="6" t="n"/>
-      <c r="I43" s="6" t="n"/>
+    <row r="43">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>4.11</t>
+        </is>
+      </c>
+      <c r="B43" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　令和8年度の基本料金等免除の確認</t>
+        </is>
+      </c>
+      <c r="C43" s="8" t="inlineStr">
+        <is>
+          <t>免除の整理</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>町</t>
+        </is>
+      </c>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="F43" s="7" t="inlineStr">
+        <is>
+          <t>R8.11</t>
+        </is>
+      </c>
+      <c r="G43" s="14" t="inlineStr">
+        <is>
+          <t>町回答待ち</t>
+        </is>
+      </c>
+      <c r="H43" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" s="15" t="inlineStr">
+        <is>
+          <t>★令和8年4〜6月請求分の免除。調定減と交付金等による補填の内訳が必要</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">　パターン1　現行体系維持案</t>
+          <t xml:space="preserve">　令和8・9年度の収入の橋渡し</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>パターン1試算</t>
+          <t>年度別収入表</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
@@ -2307,7 +2333,7 @@
       </c>
       <c r="E44" s="7" t="inlineStr">
         <is>
-          <t>R8.6</t>
+          <t>R8.11</t>
         </is>
       </c>
       <c r="F44" s="7" t="inlineStr">
@@ -2315,79 +2341,53 @@
           <t>R8.12</t>
         </is>
       </c>
-      <c r="G44" s="9" t="inlineStr">
-        <is>
-          <t>進行中</t>
+      <c r="G44" s="13" t="inlineStr">
+        <is>
+          <t>未着手</t>
         </is>
       </c>
       <c r="H44" s="10" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="I44" s="8" t="inlineStr">
-        <is>
-          <t>仕様書要求。確定値による再算定が残る</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="7" t="inlineStr">
-        <is>
-          <t>5.2</t>
-        </is>
-      </c>
-      <c r="B45" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　パターン2　赤字半減案</t>
-        </is>
-      </c>
-      <c r="C45" s="8" t="inlineStr">
-        <is>
-          <t>パターン2試算</t>
-        </is>
-      </c>
-      <c r="D45" s="7" t="inlineStr">
-        <is>
-          <t>当方</t>
-        </is>
-      </c>
-      <c r="E45" s="7" t="inlineStr">
-        <is>
-          <t>R8.6</t>
-        </is>
-      </c>
-      <c r="F45" s="7" t="inlineStr">
-        <is>
-          <t>R8.12</t>
-        </is>
-      </c>
-      <c r="G45" s="9" t="inlineStr">
-        <is>
-          <t>進行中</t>
-        </is>
-      </c>
-      <c r="H45" s="10" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="I45" s="8" t="inlineStr">
-        <is>
-          <t>仕様書要求。「現状赤字額」の定義を町と確認する必要がある</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I44" s="15" t="inlineStr">
+        <is>
+          <t>★免除と適用開始時期を織り込んだ実収入。4.11が前提</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="19" customHeight="1">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>料金改定シミュレーション</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="n"/>
+      <c r="D45" s="6" t="n"/>
+      <c r="E45" s="6" t="n"/>
+      <c r="F45" s="6" t="n"/>
+      <c r="G45" s="6" t="n"/>
+      <c r="H45" s="6" t="n"/>
+      <c r="I45" s="6" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">　パターン3-A　口径別標準逓増案</t>
+          <t xml:space="preserve">　パターン1　現行体系維持案</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>料金表案3-A</t>
+          <t>パターン1試算</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="F46" s="7" t="inlineStr">
         <is>
-          <t>R9.1</t>
+          <t>R8.12</t>
         </is>
       </c>
       <c r="G46" s="9" t="inlineStr">
@@ -2411,28 +2411,28 @@
         </is>
       </c>
       <c r="H46" s="10" t="n">
-        <v>0.7</v>
+        <v>0.85</v>
       </c>
       <c r="I46" s="8" t="inlineStr">
         <is>
-          <t>仕様書要求。実調定による検証が未了</t>
+          <t>仕様書要求。確定値による再算定が残る</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">　パターン3-B　産業配慮案</t>
+          <t xml:space="preserve">　パターン2　赤字半減案</t>
         </is>
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>料金表案3-B</t>
+          <t>パターン2試算</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
@@ -2447,7 +2447,7 @@
       </c>
       <c r="F47" s="7" t="inlineStr">
         <is>
-          <t>R9.1</t>
+          <t>R8.12</t>
         </is>
       </c>
       <c r="G47" s="9" t="inlineStr">
@@ -2456,28 +2456,28 @@
         </is>
       </c>
       <c r="H47" s="10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I47" s="15" t="inlineStr">
-        <is>
-          <t>★境界で料金が約6割下がる逆転がある。適用方式が未決定</t>
+        <v>0.8</v>
+      </c>
+      <c r="I47" s="8" t="inlineStr">
+        <is>
+          <t>仕様書要求。「現状赤字額」の定義を町と確認する必要がある</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">　A〜E案の比較</t>
+          <t xml:space="preserve">　パターン3-A　口径別標準逓増案</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>比較表</t>
+          <t>料金表案3-A</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>R8.7</t>
+          <t>R8.6</t>
         </is>
       </c>
       <c r="F48" s="7" t="inlineStr">
@@ -2501,24 +2501,28 @@
         </is>
       </c>
       <c r="H48" s="10" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="I48" s="8" t="inlineStr"/>
+        <v>0.7</v>
+      </c>
+      <c r="I48" s="8" t="inlineStr">
+        <is>
+          <t>仕様書要求。実調定による検証が未了</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">　段階改定・経過措置の設計</t>
+          <t xml:space="preserve">　パターン3-B　産業配慮案</t>
         </is>
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>経過措置案</t>
+          <t>料金表案3-B</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
@@ -2528,7 +2532,7 @@
       </c>
       <c r="E49" s="7" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.6</t>
         </is>
       </c>
       <c r="F49" s="7" t="inlineStr">
@@ -2542,28 +2546,28 @@
         </is>
       </c>
       <c r="H49" s="10" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="I49" s="8" t="inlineStr">
-        <is>
-          <t>枠組みは整理済み。具体設計は改定案の決定後</t>
+        <v>0.5</v>
+      </c>
+      <c r="I49" s="15" t="inlineStr">
+        <is>
+          <t>★境界で料金が約6割下がる逆転がある。適用方式が未決定</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">　年次の資金収支の作成</t>
+          <t xml:space="preserve">　A〜E案の比較</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>資金収支表</t>
+          <t>比較表</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
@@ -2573,7 +2577,7 @@
       </c>
       <c r="E50" s="7" t="inlineStr">
         <is>
-          <t>R8.12</t>
+          <t>R8.7</t>
         </is>
       </c>
       <c r="F50" s="7" t="inlineStr">
@@ -2581,34 +2585,30 @@
           <t>R9.1</t>
         </is>
       </c>
-      <c r="G50" s="13" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="G50" s="9" t="inlineStr">
+        <is>
+          <t>進行中</t>
         </is>
       </c>
       <c r="H50" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I50" s="15" t="inlineStr">
-        <is>
-          <t>★初年度の適用月数・期首資金・元金償還を含む。改定時期の判断に必要</t>
-        </is>
-      </c>
+        <v>0.85</v>
+      </c>
+      <c r="I50" s="8" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="7" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">　感応度分析</t>
+          <t xml:space="preserve">　段階改定・経過措置の設計</t>
         </is>
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>感応度表</t>
+          <t>経過措置案</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
@@ -2618,191 +2618,191 @@
       </c>
       <c r="E51" s="7" t="inlineStr">
         <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="F51" s="7" t="inlineStr">
+        <is>
+          <t>R9.1</t>
+        </is>
+      </c>
+      <c r="G51" s="9" t="inlineStr">
+        <is>
+          <t>進行中</t>
+        </is>
+      </c>
+      <c r="H51" s="10" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I51" s="8" t="inlineStr">
+        <is>
+          <t>枠組みは整理済み。具体設計は改定案の決定後</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="7" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
+      <c r="B52" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　年次の資金収支の作成</t>
+        </is>
+      </c>
+      <c r="C52" s="8" t="inlineStr">
+        <is>
+          <t>資金収支表</t>
+        </is>
+      </c>
+      <c r="D52" s="7" t="inlineStr">
+        <is>
+          <t>当方</t>
+        </is>
+      </c>
+      <c r="E52" s="7" t="inlineStr">
+        <is>
           <t>R8.12</t>
         </is>
       </c>
-      <c r="F51" s="7" t="inlineStr">
+      <c r="F52" s="7" t="inlineStr">
         <is>
           <t>R9.1</t>
         </is>
       </c>
-      <c r="G51" s="9" t="inlineStr">
-        <is>
-          <t>進行中</t>
-        </is>
-      </c>
-      <c r="H51" s="10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I51" s="8" t="inlineStr">
-        <is>
-          <t>主要5条件は整理済み。需要減・金利・工事費が未了</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="19" customHeight="1">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B52" s="5" t="inlineStr">
-        <is>
-          <t>利用者への影響分析</t>
-        </is>
-      </c>
-      <c r="C52" s="6" t="n"/>
-      <c r="D52" s="6" t="n"/>
-      <c r="E52" s="6" t="n"/>
-      <c r="F52" s="6" t="n"/>
-      <c r="G52" s="6" t="n"/>
-      <c r="H52" s="6" t="n"/>
-      <c r="I52" s="6" t="n"/>
+      <c r="G52" s="13" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="H52" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" s="15" t="inlineStr">
+        <is>
+          <t>★適用開始は令和9年4月以降。初年度の適用月数・期首資金・元金償還を含む</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="7" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">　使用者別調定明細の受領</t>
+          <t xml:space="preserve">　感応度分析</t>
         </is>
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t>調定明細</t>
+          <t>感応度表</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>町</t>
+          <t>当方</t>
         </is>
       </c>
       <c r="E53" s="7" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.12</t>
         </is>
       </c>
       <c r="F53" s="7" t="inlineStr">
         <is>
-          <t>R8.11</t>
-        </is>
-      </c>
-      <c r="G53" s="14" t="inlineStr">
-        <is>
-          <t>町回答待ち</t>
+          <t>R9.1</t>
+        </is>
+      </c>
+      <c r="G53" s="9" t="inlineStr">
+        <is>
+          <t>進行中</t>
         </is>
       </c>
       <c r="H53" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I53" s="15" t="inlineStr">
-        <is>
-          <t>★6.2〜6.5すべての前提。これがないと代表値推計どまり</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="7" t="inlineStr">
-        <is>
-          <t>6.2</t>
-        </is>
-      </c>
-      <c r="B54" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　水量ゾーン別の影響</t>
-        </is>
-      </c>
-      <c r="C54" s="8" t="inlineStr">
-        <is>
-          <t>影響試算</t>
-        </is>
-      </c>
-      <c r="D54" s="7" t="inlineStr">
-        <is>
-          <t>当方</t>
-        </is>
-      </c>
-      <c r="E54" s="7" t="inlineStr">
-        <is>
-          <t>R8.7</t>
-        </is>
-      </c>
-      <c r="F54" s="7" t="inlineStr">
-        <is>
-          <t>R8.12</t>
-        </is>
-      </c>
-      <c r="G54" s="9" t="inlineStr">
-        <is>
-          <t>進行中</t>
-        </is>
-      </c>
-      <c r="H54" s="10" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="I54" s="8" t="inlineStr">
-        <is>
-          <t>代表値による推計。件数の原票照合が未了</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="I53" s="8" t="inlineStr">
+        <is>
+          <t>主要5条件は整理済み。需要減・金利・工事費が未了</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="19" customHeight="1">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>利用者への影響分析</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="n"/>
+      <c r="D54" s="6" t="n"/>
+      <c r="E54" s="6" t="n"/>
+      <c r="F54" s="6" t="n"/>
+      <c r="G54" s="6" t="n"/>
+      <c r="H54" s="6" t="n"/>
+      <c r="I54" s="6" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="7" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">　口径別の影響</t>
+          <t xml:space="preserve">　使用者別調定明細の受領</t>
         </is>
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t>影響試算</t>
+          <t>調定明細</t>
         </is>
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>当方</t>
+          <t>町</t>
         </is>
       </c>
       <c r="E55" s="7" t="inlineStr">
         <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="F55" s="7" t="inlineStr">
+        <is>
           <t>R8.11</t>
         </is>
       </c>
-      <c r="F55" s="7" t="inlineStr">
-        <is>
-          <t>R8.12</t>
-        </is>
-      </c>
-      <c r="G55" s="9" t="inlineStr">
-        <is>
-          <t>進行中</t>
+      <c r="G55" s="14" t="inlineStr">
+        <is>
+          <t>町回答待ち</t>
         </is>
       </c>
       <c r="H55" s="10" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="I55" s="8" t="inlineStr">
-        <is>
-          <t>倍率表は作成済み。実際の口径分布を反映していない</t>
+        <v>0</v>
+      </c>
+      <c r="I55" s="15" t="inlineStr">
+        <is>
+          <t>★6.2〜6.5すべての前提。これがないと代表値推計どまり</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>6.2</t>
         </is>
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">　水産加工業への影響</t>
+          <t xml:space="preserve">　水量ゾーン別の影響</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
@@ -2831,23 +2831,23 @@
         </is>
       </c>
       <c r="H56" s="10" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="I56" s="8" t="inlineStr">
         <is>
-          <t>仮定した事例のみ。合計額・減収額は算定できていない</t>
+          <t>代表値による推計。件数の原票照合が未了</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="7" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">　特殊用途区分への影響</t>
+          <t xml:space="preserve">　口径別の影響</t>
         </is>
       </c>
       <c r="C57" s="8" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="E57" s="7" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.11</t>
         </is>
       </c>
       <c r="F57" s="7" t="inlineStr">
@@ -2876,28 +2876,28 @@
         </is>
       </c>
       <c r="H57" s="10" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="I57" s="8" t="inlineStr">
         <is>
-          <t>湯屋用・直接船舶は試算済み。委託船舶が未試算</t>
+          <t>倍率表は作成済み。実際の口径分布を反映していない</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
         <is>
-          <t>6.6</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">　値上げ・値下げ件数の集計</t>
+          <t xml:space="preserve">　水産加工業への影響</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>件数集計</t>
+          <t>影響試算</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
@@ -2907,61 +2907,87 @@
       </c>
       <c r="E58" s="7" t="inlineStr">
         <is>
+          <t>R8.7</t>
+        </is>
+      </c>
+      <c r="F58" s="7" t="inlineStr">
+        <is>
           <t>R8.12</t>
         </is>
       </c>
-      <c r="F58" s="7" t="inlineStr">
-        <is>
-          <t>R9.1</t>
-        </is>
-      </c>
-      <c r="G58" s="13" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="G58" s="9" t="inlineStr">
+        <is>
+          <t>進行中</t>
         </is>
       </c>
       <c r="H58" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" s="15" t="inlineStr">
-        <is>
-          <t>★住民説明で必ず問われる。6.1が前提</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="19" customHeight="1">
-      <c r="A59" s="5" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B59" s="5" t="inlineStr">
-        <is>
-          <t>対外説明資料</t>
-        </is>
-      </c>
-      <c r="C59" s="6" t="n"/>
-      <c r="D59" s="6" t="n"/>
-      <c r="E59" s="6" t="n"/>
-      <c r="F59" s="6" t="n"/>
-      <c r="G59" s="6" t="n"/>
-      <c r="H59" s="6" t="n"/>
-      <c r="I59" s="6" t="n"/>
+        <v>0.4</v>
+      </c>
+      <c r="I58" s="8" t="inlineStr">
+        <is>
+          <t>仮定した事例のみ。合計額・減収額は算定できていない</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="7" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="B59" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　特殊用途区分への影響</t>
+        </is>
+      </c>
+      <c r="C59" s="8" t="inlineStr">
+        <is>
+          <t>影響試算</t>
+        </is>
+      </c>
+      <c r="D59" s="7" t="inlineStr">
+        <is>
+          <t>当方</t>
+        </is>
+      </c>
+      <c r="E59" s="7" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="F59" s="7" t="inlineStr">
+        <is>
+          <t>R8.12</t>
+        </is>
+      </c>
+      <c r="G59" s="9" t="inlineStr">
+        <is>
+          <t>進行中</t>
+        </is>
+      </c>
+      <c r="H59" s="10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I59" s="8" t="inlineStr">
+        <is>
+          <t>湯屋用・直接船舶は試算済み。委託船舶が未試算</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>6.6</t>
         </is>
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">　住民・議会説明用の要約</t>
+          <t xml:space="preserve">　値上げ・値下げ件数の集計</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>中間報告書第11章</t>
+          <t>件数集計</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
@@ -2971,87 +2997,61 @@
       </c>
       <c r="E60" s="7" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.12</t>
         </is>
       </c>
       <c r="F60" s="7" t="inlineStr">
         <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G60" s="11" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="H60" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I60" s="8" t="inlineStr">
-        <is>
-          <t>仕様書要求の「切り抜いて使用できる体裁」</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="7" t="inlineStr">
-        <is>
-          <t>7.2</t>
-        </is>
-      </c>
-      <c r="B61" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　住民説明会資料</t>
-        </is>
-      </c>
-      <c r="C61" s="8" t="inlineStr">
-        <is>
-          <t>説明会資料</t>
-        </is>
-      </c>
-      <c r="D61" s="7" t="inlineStr">
-        <is>
-          <t>当方</t>
-        </is>
-      </c>
-      <c r="E61" s="7" t="inlineStr">
-        <is>
           <t>R9.1</t>
         </is>
       </c>
-      <c r="F61" s="7" t="inlineStr">
-        <is>
-          <t>R9.1</t>
-        </is>
-      </c>
-      <c r="G61" s="13" t="inlineStr">
+      <c r="G60" s="13" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="H61" s="10" t="n">
+      <c r="H60" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="I61" s="8" t="inlineStr">
-        <is>
-          <t>図表中心の別資料</t>
-        </is>
-      </c>
+      <c r="I60" s="15" t="inlineStr">
+        <is>
+          <t>★住民説明で必ず問われる。6.1が前提</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="19" customHeight="1">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>対外説明資料</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="n"/>
+      <c r="D61" s="6" t="n"/>
+      <c r="E61" s="6" t="n"/>
+      <c r="F61" s="6" t="n"/>
+      <c r="G61" s="6" t="n"/>
+      <c r="H61" s="6" t="n"/>
+      <c r="I61" s="6" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="7" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">　議会説明資料</t>
+          <t xml:space="preserve">　住民・議会説明用の要約</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>議会資料</t>
+          <t>中間報告書第11章</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
@@ -3061,38 +3061,42 @@
       </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
-          <t>R9.2</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="F62" s="7" t="inlineStr">
         <is>
-          <t>R9.2</t>
-        </is>
-      </c>
-      <c r="G62" s="13" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="H62" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I62" s="8" t="inlineStr"/>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="G62" s="11" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="H62" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I62" s="8" t="inlineStr">
+        <is>
+          <t>仕様書要求の「切り抜いて使用できる体裁」</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="7" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">　水産加工業者向け資料</t>
+          <t xml:space="preserve">　住民説明会資料</t>
         </is>
       </c>
       <c r="C63" s="8" t="inlineStr">
         <is>
-          <t>事業者資料</t>
+          <t>説明会資料</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
@@ -3118,22 +3122,26 @@
       <c r="H63" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="I63" s="8" t="inlineStr"/>
+      <c r="I63" s="8" t="inlineStr">
+        <is>
+          <t>図表中心の別資料</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="B64" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">　条例改正の参考資料</t>
+          <t xml:space="preserve">　議会説明資料</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t>新旧対照・条文例</t>
+          <t>議会資料</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
@@ -3161,39 +3169,61 @@
       </c>
       <c r="I64" s="8" t="inlineStr"/>
     </row>
-    <row r="65" ht="19" customHeight="1">
-      <c r="A65" s="5" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B65" s="5" t="inlineStr">
-        <is>
-          <t>参考整理（県内比較）</t>
-        </is>
-      </c>
-      <c r="C65" s="6" t="n"/>
-      <c r="D65" s="6" t="n"/>
-      <c r="E65" s="6" t="n"/>
-      <c r="F65" s="6" t="n"/>
-      <c r="G65" s="6" t="n"/>
-      <c r="H65" s="6" t="n"/>
-      <c r="I65" s="6" t="n"/>
+    <row r="65">
+      <c r="A65" s="7" t="inlineStr">
+        <is>
+          <t>7.4</t>
+        </is>
+      </c>
+      <c r="B65" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　水産加工業者向け資料</t>
+        </is>
+      </c>
+      <c r="C65" s="8" t="inlineStr">
+        <is>
+          <t>事業者資料</t>
+        </is>
+      </c>
+      <c r="D65" s="7" t="inlineStr">
+        <is>
+          <t>当方</t>
+        </is>
+      </c>
+      <c r="E65" s="7" t="inlineStr">
+        <is>
+          <t>R9.1</t>
+        </is>
+      </c>
+      <c r="F65" s="7" t="inlineStr">
+        <is>
+          <t>R9.1</t>
+        </is>
+      </c>
+      <c r="G65" s="13" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="H65" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" s="8" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">　県内他団体の料金比較</t>
+          <t xml:space="preserve">　条例改正の参考資料</t>
         </is>
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t>比較資料</t>
+          <t>新旧対照・条文例</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
@@ -3203,87 +3233,57 @@
       </c>
       <c r="E66" s="7" t="inlineStr">
         <is>
-          <t>R8.5</t>
+          <t>R9.2</t>
         </is>
       </c>
       <c r="F66" s="7" t="inlineStr">
         <is>
-          <t>R8.7</t>
-        </is>
-      </c>
-      <c r="G66" s="11" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="H66" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I66" s="8" t="inlineStr">
-        <is>
-          <t>気仙沼市・石巻広域・塩竈市を公式料金表と突合済み</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="7" t="inlineStr">
-        <is>
-          <t>8.2</t>
-        </is>
-      </c>
-      <c r="B67" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　南三陸町の口径別料金の照会</t>
-        </is>
-      </c>
-      <c r="C67" s="8" t="inlineStr">
-        <is>
-          <t>料金表</t>
-        </is>
-      </c>
-      <c r="D67" s="7" t="inlineStr">
-        <is>
-          <t>当方</t>
-        </is>
-      </c>
-      <c r="E67" s="7" t="inlineStr">
-        <is>
-          <t>R8.8</t>
-        </is>
-      </c>
-      <c r="F67" s="7" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="G67" s="13" t="inlineStr">
+          <t>R9.2</t>
+        </is>
+      </c>
+      <c r="G66" s="13" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="H67" s="10" t="n">
+      <c r="H66" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="I67" s="15" t="inlineStr">
-        <is>
-          <t>★令和8年8月3日に「次に実施」とされたまま。13mm以外が未取得</t>
-        </is>
-      </c>
+      <c r="I66" s="8" t="inlineStr"/>
+    </row>
+    <row r="67" ht="19" customHeight="1">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>参考整理（県内比較）</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="n"/>
+      <c r="D67" s="6" t="n"/>
+      <c r="E67" s="6" t="n"/>
+      <c r="F67" s="6" t="n"/>
+      <c r="G67" s="6" t="n"/>
+      <c r="H67" s="6" t="n"/>
+      <c r="I67" s="6" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="7" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="B68" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">　県内料金体系統一化の検討</t>
+          <t xml:space="preserve">　県内他団体の料金比較</t>
         </is>
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t>検討資料6点</t>
+          <t>比較資料</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
@@ -3298,7 +3298,7 @@
       </c>
       <c r="F68" s="7" t="inlineStr">
         <is>
-          <t>R8.8</t>
+          <t>R8.7</t>
         </is>
       </c>
       <c r="G68" s="11" t="inlineStr">
@@ -3311,43 +3311,69 @@
       </c>
       <c r="I68" s="8" t="inlineStr">
         <is>
-          <t>最終報告に参考として添付</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="19" customHeight="1">
-      <c r="A69" s="5" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B69" s="5" t="inlineStr">
-        <is>
-          <t>品質管理・根拠資料の整備</t>
-        </is>
-      </c>
-      <c r="C69" s="6" t="n"/>
-      <c r="D69" s="6" t="n"/>
-      <c r="E69" s="6" t="n"/>
-      <c r="F69" s="6" t="n"/>
-      <c r="G69" s="6" t="n"/>
-      <c r="H69" s="6" t="n"/>
-      <c r="I69" s="6" t="n"/>
+          <t>気仙沼市・石巻広域・塩竈市を公式料金表と突合済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="7" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
+      </c>
+      <c r="B69" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　南三陸町の口径別料金の照会</t>
+        </is>
+      </c>
+      <c r="C69" s="8" t="inlineStr">
+        <is>
+          <t>料金表</t>
+        </is>
+      </c>
+      <c r="D69" s="7" t="inlineStr">
+        <is>
+          <t>当方</t>
+        </is>
+      </c>
+      <c r="E69" s="7" t="inlineStr">
+        <is>
+          <t>R8.8</t>
+        </is>
+      </c>
+      <c r="F69" s="7" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G69" s="13" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="H69" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" s="15" t="inlineStr">
+        <is>
+          <t>★令和8年8月3日に「次に実施」とされたまま。13mm以外が未取得</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">　成果品Excelの不整合の修正</t>
+          <t xml:space="preserve">　県内料金体系統一化の検討</t>
         </is>
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t>修正済Excel</t>
+          <t>検討資料6点</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
@@ -3357,87 +3383,61 @@
       </c>
       <c r="E70" s="7" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.5</t>
         </is>
       </c>
       <c r="F70" s="7" t="inlineStr">
         <is>
-          <t>R8.11</t>
-        </is>
-      </c>
-      <c r="G70" s="13" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="H70" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I70" s="15" t="inlineStr">
-        <is>
-          <t>★令和8年9月8日に6件を検出したまま未修正。最新の指摘でも再現用として使えないと再指摘</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="7" t="inlineStr">
-        <is>
-          <t>9.2</t>
-        </is>
-      </c>
-      <c r="B71" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　経営戦略シミュレーションの参照エラーの修復</t>
-        </is>
-      </c>
-      <c r="C71" s="8" t="inlineStr">
-        <is>
-          <t>修復記録</t>
-        </is>
-      </c>
-      <c r="D71" s="7" t="inlineStr">
-        <is>
-          <t>当方</t>
-        </is>
-      </c>
-      <c r="E71" s="7" t="inlineStr">
-        <is>
-          <t>R8.11</t>
-        </is>
-      </c>
-      <c r="F71" s="7" t="inlineStr">
-        <is>
-          <t>R8.12</t>
-        </is>
-      </c>
-      <c r="G71" s="13" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="H71" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I71" s="15" t="inlineStr">
-        <is>
-          <t>★参照エラーが残る。最終報告で再利用するなら修復が必要</t>
-        </is>
-      </c>
+          <t>R8.8</t>
+        </is>
+      </c>
+      <c r="G70" s="11" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="H70" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I70" s="8" t="inlineStr">
+        <is>
+          <t>最終報告に参考として添付</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="19" customHeight="1">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>品質管理・根拠資料の整備</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="n"/>
+      <c r="D71" s="6" t="n"/>
+      <c r="E71" s="6" t="n"/>
+      <c r="F71" s="6" t="n"/>
+      <c r="G71" s="6" t="n"/>
+      <c r="H71" s="6" t="n"/>
+      <c r="I71" s="6" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="7" t="inlineStr">
         <is>
-          <t>9.3</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="B72" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">　採用資料の一本化と出所表記</t>
+          <t xml:space="preserve">　採用計算表の整備</t>
         </is>
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t>出所一覧</t>
+          <t>採用計算表</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
@@ -3447,42 +3447,42 @@
       </c>
       <c r="E72" s="7" t="inlineStr">
         <is>
-          <t>R8.12</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="F72" s="7" t="inlineStr">
         <is>
-          <t>R9.2</t>
-        </is>
-      </c>
-      <c r="G72" s="13" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="H72" s="10" t="n">
-        <v>0</v>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="G72" s="11" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="H72" s="12" t="n">
+        <v>1</v>
       </c>
       <c r="I72" s="8" t="inlineStr">
         <is>
-          <t>各数値に採用版・対象年度・税区分・原票・確認者・確認日を付す</t>
+          <t>本文の全指標を再現する7シート。07_本文照合表で18項目の一致を確認</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="7" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="B73" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">　成果品の作成者情報の統一</t>
+          <t xml:space="preserve">　成果品Excelの不整合の修正</t>
         </is>
       </c>
       <c r="C73" s="8" t="inlineStr">
         <is>
-          <t>成果品19点</t>
+          <t>修正済Excel</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
@@ -3497,131 +3497,311 @@
       </c>
       <c r="F73" s="7" t="inlineStr">
         <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G73" s="11" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="H73" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I73" s="8" t="inlineStr"/>
+          <t>R8.11</t>
+        </is>
+      </c>
+      <c r="G73" s="9" t="inlineStr">
+        <is>
+          <t>進行中</t>
+        </is>
+      </c>
+      <c r="H73" s="10" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I73" s="15" t="inlineStr">
+        <is>
+          <t>★令和8年9月8日に6件を検出したまま未修正。最新の指摘でも再現用として使えないと再指摘</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="inlineStr">
         <is>
+          <t>9.2</t>
+        </is>
+      </c>
+      <c r="B74" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　経営戦略シミュレーションの参照エラーの修復</t>
+        </is>
+      </c>
+      <c r="C74" s="8" t="inlineStr">
+        <is>
+          <t>修復記録</t>
+        </is>
+      </c>
+      <c r="D74" s="7" t="inlineStr">
+        <is>
+          <t>当方</t>
+        </is>
+      </c>
+      <c r="E74" s="7" t="inlineStr">
+        <is>
+          <t>R8.11</t>
+        </is>
+      </c>
+      <c r="F74" s="7" t="inlineStr">
+        <is>
+          <t>R8.12</t>
+        </is>
+      </c>
+      <c r="G74" s="13" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="H74" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I74" s="15" t="inlineStr">
+        <is>
+          <t>★参照エラーが残る。最終報告で再利用するなら修復が必要</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="7" t="inlineStr">
+        <is>
+          <t>9.3</t>
+        </is>
+      </c>
+      <c r="B75" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　採用資料の一本化と出所表記</t>
+        </is>
+      </c>
+      <c r="C75" s="8" t="inlineStr">
+        <is>
+          <t>出所一覧</t>
+        </is>
+      </c>
+      <c r="D75" s="7" t="inlineStr">
+        <is>
+          <t>当方</t>
+        </is>
+      </c>
+      <c r="E75" s="7" t="inlineStr">
+        <is>
+          <t>R8.12</t>
+        </is>
+      </c>
+      <c r="F75" s="7" t="inlineStr">
+        <is>
+          <t>R9.2</t>
+        </is>
+      </c>
+      <c r="G75" s="13" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="H75" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I75" s="8" t="inlineStr">
+        <is>
+          <t>各数値に採用版・対象年度・税区分・原票・確認者・確認日を付す</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="7" t="inlineStr">
+        <is>
+          <t>9.4</t>
+        </is>
+      </c>
+      <c r="B76" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　成果品の作成者情報の統一</t>
+        </is>
+      </c>
+      <c r="C76" s="8" t="inlineStr">
+        <is>
+          <t>成果品19点</t>
+        </is>
+      </c>
+      <c r="D76" s="7" t="inlineStr">
+        <is>
+          <t>当方</t>
+        </is>
+      </c>
+      <c r="E76" s="7" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="F76" s="7" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="G76" s="11" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="H76" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I76" s="8" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="7" t="inlineStr">
+        <is>
           <t>9.5</t>
         </is>
       </c>
-      <c r="B74" s="8" t="inlineStr">
+      <c r="B77" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">　受け渡し用パッケージの整備</t>
         </is>
       </c>
-      <c r="C74" s="8" t="inlineStr">
+      <c r="C77" s="8" t="inlineStr">
         <is>
           <t>zip一式</t>
         </is>
       </c>
-      <c r="D74" s="7" t="inlineStr">
-        <is>
-          <t>当方</t>
-        </is>
-      </c>
-      <c r="E74" s="7" t="inlineStr">
+      <c r="D77" s="7" t="inlineStr">
+        <is>
+          <t>当方</t>
+        </is>
+      </c>
+      <c r="E77" s="7" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="F74" s="7" t="inlineStr">
+      <c r="F77" s="7" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G74" s="11" t="inlineStr">
+      <c r="G77" s="11" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="H74" s="12" t="n">
+      <c r="H77" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I74" s="8" t="inlineStr">
-        <is>
-          <t>ファイル名は半角英数字・対応表を同梱</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="B76" s="16" t="inlineStr">
+      <c r="I77" s="8" t="inlineStr">
+        <is>
+          <t>ファイル名は半角英数字・対応表を同梱。旧版は使用不可として別フォルダに分離</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="7" t="inlineStr">
+        <is>
+          <t>9.6</t>
+        </is>
+      </c>
+      <c r="B78" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　実施時期と表現の統一</t>
+        </is>
+      </c>
+      <c r="C78" s="8" t="inlineStr">
+        <is>
+          <t>改訂版一式</t>
+        </is>
+      </c>
+      <c r="D78" s="7" t="inlineStr">
+        <is>
+          <t>当方</t>
+        </is>
+      </c>
+      <c r="E78" s="7" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="F78" s="7" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="G78" s="11" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="H78" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I78" s="8" t="inlineStr">
+        <is>
+          <t>議決と適用開始の分離、1.99倍と3-Aの100％の位置づけ、3-Bの未設計の明示</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" s="16" t="inlineStr">
         <is>
           <t>状態別の件数</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="B77" s="17" t="inlineStr">
+    <row r="81">
+      <c r="B81" s="17" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="C77" s="18" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="B78" s="19" t="inlineStr">
+      <c r="C81" s="18" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" s="19" t="inlineStr">
         <is>
           <t>進行中</t>
         </is>
       </c>
-      <c r="C78" s="18" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="B79" s="20" t="inlineStr">
+      <c r="C82" s="18" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" s="20" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="C79" s="18" t="n">
+      <c r="C83" s="18" t="n">
         <v>22</v>
       </c>
     </row>
-    <row r="80">
-      <c r="B80" s="21" t="inlineStr">
+    <row r="84">
+      <c r="B84" s="21" t="inlineStr">
         <is>
           <t>町回答待ち</t>
         </is>
       </c>
-      <c r="C80" s="18" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="B81" s="22" t="inlineStr">
+      <c r="C84" s="18" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" s="22" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="C81" s="23" t="n">
-        <v>60</v>
-      </c>
-      <c r="D81" s="24" t="inlineStr">
+      <c r="C85" s="23" t="n">
+        <v>64</v>
+      </c>
+      <c r="D85" s="24" t="inlineStr">
         <is>
           <t>全体進捗</t>
         </is>
       </c>
-      <c r="E81" s="25" t="n">
-        <v>0.43</v>
+      <c r="E85" s="25" t="n">
+        <v>0.4390625</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:I74"/>
+  <autoFilter ref="A5:I78"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3632,7 +3812,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3909,7 +4089,7 @@
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
-          <t>①中間報告の確定数値に合わせて02〜08の各ブックを再生成する　②再生成の手順を残し、確定値の差替えを1回で通せるようにする</t>
+          <t>①採用計算表を作成し、本文の18項目が一致することを確認した（実施済）　②受け渡し用zipでは旧版を使用不可として別フォルダに分離した（実施済）　③残りは、旧版の各ブック自体を確定数値で再生成すること</t>
         </is>
       </c>
       <c r="H9" s="26" t="inlineStr">
@@ -3921,79 +4101,79 @@
     <row r="10">
       <c r="A10" s="26" t="inlineStr">
         <is>
-          <t>S6</t>
+          <t>S9</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>停滞</t>
+          <t>町回答待ち</t>
         </is>
       </c>
       <c r="C10" s="27" t="inlineStr">
         <is>
-          <t>南三陸町の口径別料金の照会が未着手（WBS 8.2）</t>
+          <t>令和8年度の基本料金等の免除が数値に反映されていない（WBS 4.11・4.12）</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>R8.8.3</t>
+          <t>R8.9.28</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>約2か月</t>
+          <t>判明したところ</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>引継ぎメモで「次に実施すべき作業」に挙がったまま。20mm以上の口径が公表されておらず、県内比較表が13mmで止まっている。口径別料金表案の水準設定の根拠が1団体分薄い。</t>
+          <t>令和8年4〜6月請求分について、官公庁等を除き上水道の基本料金とメーター使用料を免除する措置がとられているとの情報を得た。財源は国の物価高騰対応重点支援地方創生臨時交付金とされる。原典は当方で確認できていない。本報告の給水収益は経営戦略の見込額をそのまま用いており、免除による調定減も交付金等による補填収入も織り込んでいない。令和8年度を基準年度として扱う場合や資金残高を示す場合に影響する。</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
-          <t>①南三陸町上下水道事業所へ電話またはメールで照会（所要1日）</t>
+          <t>①免除の内容（対象・免除額・件数）と補填収入の額・会計処理を町に確認する　②令和8年度・令和9年度の収入の橋渡し表を作る</t>
         </is>
       </c>
       <c r="H10" s="26" t="inlineStr">
         <is>
-          <t>R8.10上旬</t>
+          <t>R8.11末</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="26" t="inlineStr">
         <is>
-          <t>S7</t>
+          <t>S6</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>未入手</t>
+          <t>停滞</t>
         </is>
       </c>
       <c r="C11" s="27" t="inlineStr">
         <is>
-          <t>業務仕様書の原本が手元にない（WBS 1.7）</t>
+          <t>南三陸町の口径別料金の照会が未着手（WBS 8.2）</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>R8.8.3</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>着手なし</t>
+          <t>約2か月</t>
         </is>
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
-          <t>照合できているのは令和8年6月2日の要約のみ。資産維持率3％の要求水準、「現状赤字額」の定義、報告様式の要件が確認できていない。3パターンの体裁が要求に対応していることは確認できるが、履行要件を満たすとの最終判定ができない。</t>
+          <t>引継ぎメモで「次に実施すべき作業」に挙がったまま。20mm以上の口径が公表されておらず、県内比較表が13mmで止まっている。口径別料金表案の水準設定の根拠が1団体分薄い。</t>
         </is>
       </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
-          <t>①町から仕様書の写しを受領する　②受領後、要求事項と成果物の対応表を作る</t>
+          <t>①南三陸町上下水道事業所へ電話またはメールで照会（所要1日）</t>
         </is>
       </c>
       <c r="H11" s="26" t="inlineStr">
@@ -4005,115 +4185,130 @@
     <row r="12">
       <c r="A12" s="26" t="inlineStr">
         <is>
+          <t>S7</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>未入手</t>
+        </is>
+      </c>
+      <c r="C12" s="27" t="inlineStr">
+        <is>
+          <t>業務仕様書の原本が手元にない（WBS 1.7）</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>着手なし</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>照合できているのは令和8年6月2日の要約のみ。資産維持率3％の要求水準、「現状赤字額」の定義、報告様式の要件が確認できていない。3パターンの体裁が要求に対応していることは確認できるが、履行要件を満たすとの最終判定ができない。</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>①町から仕様書の写しを受領する　②受領後、要求事項と成果物の対応表を作る</t>
+        </is>
+      </c>
+      <c r="H12" s="26" t="inlineStr">
+        <is>
+          <t>R8.10上旬</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="26" t="inlineStr">
+        <is>
           <t>S8</t>
         </is>
       </c>
-      <c r="B12" s="14" t="inlineStr">
+      <c r="B13" s="14" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="C12" s="27" t="inlineStr">
+      <c r="C13" s="27" t="inlineStr">
         <is>
           <t>年次の資金収支が未作成（WBS 5.7）</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="D13" s="7" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
+      <c r="E13" s="7" t="inlineStr">
         <is>
           <t>着手なし</t>
         </is>
       </c>
-      <c r="F12" s="8" t="inlineStr">
+      <c r="F13" s="8" t="inlineStr">
         <is>
           <t>財政効果が5年平均に倍率を掛けた通年ベースのままで、改定初年度の適用月数、期首資金、企業債元金償還を反映していない。改定時期を決める判断材料が出せない。</t>
         </is>
       </c>
-      <c r="G12" s="8" t="inlineStr">
+      <c r="G13" s="8" t="inlineStr">
         <is>
           <t>①経営戦略の財政シミュレーションの様式を流用して年次表を作る　②改定月を3案（4月・7月・10月）置いて比較する</t>
         </is>
       </c>
-      <c r="H12" s="26" t="inlineStr">
+      <c r="H13" s="26" t="inlineStr">
         <is>
           <t>R8.12末</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="28" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="28" t="inlineStr">
         <is>
           <t>リカバリの優先順位</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="4" t="inlineStr">
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>順</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>作業</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>所要</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>期限</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>効果</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>下水道データの依頼書を作成して送付</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t>半日</t>
-        </is>
-      </c>
-      <c r="D17" s="26" t="inlineStr">
-        <is>
-          <t>R8.10.9</t>
-        </is>
-      </c>
-      <c r="E17" s="8" t="inlineStr">
-        <is>
-          <t>最大の空白（S1）に着手できる。依頼から受領まで1か月かかるため最優先</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="29" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>未回答3件の再依頼書を1枚にまとめて送付（様式・期限つき）</t>
+          <t>下水道データの依頼書を作成して送付</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -4128,46 +4323,46 @@
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>S3の3件が動く。資産維持費・口径別検証・特例対象がまとめて前に進む</t>
+          <t>最大の空白（S1）に着手できる。依頼から受領まで1か月かかるため最優先</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>業務仕様書の写しの受領と対応表の作成</t>
+          <t>未回答3件の再依頼書を1枚にまとめて送付（様式・期限つき）</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>1日</t>
+          <t>半日</t>
         </is>
       </c>
       <c r="D19" s="26" t="inlineStr">
         <is>
-          <t>R8.10.16</t>
+          <t>R8.10.9</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>S7が解消し、履行要件の判定ができる</t>
+          <t>S3の3件が動く。資産維持費・口径別検証・特例対象がまとめて前に進む</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="29" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>南三陸町への料金照会</t>
+          <t>業務仕様書の写しの受領と対応表の作成</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -4177,29 +4372,29 @@
       </c>
       <c r="D20" s="26" t="inlineStr">
         <is>
-          <t>R8.10.9</t>
+          <t>R8.10.16</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>S6が解消。比較の根拠が1団体増える</t>
+          <t>S7が解消し、履行要件の判定ができる</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="29" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>調査票の未記入欄だけの確認票を送付</t>
+          <t>南三陸町への料金照会</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>半日</t>
+          <t>1日</t>
         </is>
       </c>
       <c r="D21" s="26" t="inlineStr">
@@ -4209,46 +4404,46 @@
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>S4が動く</t>
+          <t>S6が解消。比較の根拠が1団体増える</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="29" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>経営指標評価書の様式と算式の確定（水道・下水道共通）</t>
+          <t>調査票の未記入欄だけの確認票を送付</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>3日</t>
+          <t>半日</t>
         </is>
       </c>
       <c r="D22" s="26" t="inlineStr">
         <is>
-          <t>R8.10.30</t>
+          <t>R8.10.9</t>
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>S2に着手。決算確定値の受領を待たずに枠を作れる</t>
+          <t>S4が動く</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="29" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>成果品Excelを中間報告の確定数値で再生成</t>
+          <t>経営指標評価書の様式と算式の確定（水道・下水道共通）</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
@@ -4258,39 +4453,93 @@
       </c>
       <c r="D23" s="26" t="inlineStr">
         <is>
-          <t>R8.11.27</t>
+          <t>R8.10.30</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>S5が解消。町へ配布できる状態になる</t>
+          <t>S2に着手。決算確定値の受領を待たずに枠を作れる</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="29" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>成果品Excelを中間報告の確定数値で再生成</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>3日</t>
+        </is>
+      </c>
+      <c r="D24" s="26" t="inlineStr">
+        <is>
+          <t>R8.11.27</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>S5が解消。町へ配布できる状態になる</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="29" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B24" s="8" t="inlineStr">
+      <c r="B25" s="8" t="inlineStr">
         <is>
           <t>年次の資金収支の作成</t>
         </is>
       </c>
-      <c r="C24" s="7" t="inlineStr">
+      <c r="C25" s="7" t="inlineStr">
         <is>
           <t>3日</t>
         </is>
       </c>
-      <c r="D24" s="26" t="inlineStr">
+      <c r="D25" s="26" t="inlineStr">
         <is>
           <t>R8.12.25</t>
         </is>
       </c>
-      <c r="E24" s="8" t="inlineStr">
+      <c r="E25" s="8" t="inlineStr">
         <is>
           <t>S8が解消。改定時期の判断材料が出る</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="29" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>令和8年度の基本料金等免除の内容と補填の確認</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>半日</t>
+        </is>
+      </c>
+      <c r="D26" s="26" t="inlineStr">
+        <is>
+          <t>R8.10.9</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="inlineStr">
+        <is>
+          <t>S9が動く。順位2の依頼にまとめられる</t>
         </is>
       </c>
     </row>
